--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2019_valparaiso.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2019_valparaiso.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:11</t>
+    <t xml:space="preserve">2026-09-09 21:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2019_valparaiso.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2019_valparaiso.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:17</t>
+    <t xml:space="preserve">2026-09-18 09:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2019_valparaiso.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2019_valparaiso.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:12</t>
+    <t xml:space="preserve">2026-09-25 21:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2019_valparaiso.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2019_valparaiso.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 21:33</t>
+    <t xml:space="preserve">2026-10-05 02:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -612,7 +612,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>285326.62</v>
+        <v>285326.63</v>
       </c>
     </row>
     <row r="7">
